--- a/AAII_Financials/Yearly/HRT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HRT_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
   <si>
     <t>HRT</t>
   </si>
@@ -656,46 +656,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I7" s="2" t="s">
         <v>3</v>
       </c>
@@ -708,27 +708,30 @@
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>721900</v>
+      </c>
+      <c r="E8" s="3">
         <v>806700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>730100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>540200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>647600</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
@@ -741,27 +744,30 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>371700</v>
+      </c>
+      <c r="E9" s="3">
         <v>435700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>406700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>301800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>356600</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
       </c>
@@ -774,27 +780,30 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>350200</v>
+      </c>
+      <c r="E10" s="3">
         <v>370900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>323400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>238400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>291000</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
       </c>
@@ -807,9 +816,12 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,8 +835,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -855,9 +868,12 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,24 +904,27 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>1600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>24900</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,27 +940,30 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E15" s="3">
         <v>74600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>78400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>76900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>78100</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I15" s="3" t="s">
         <v>3</v>
       </c>
@@ -954,9 +976,12 @@
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,26 +992,27 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>674700</v>
+      </c>
+      <c r="E17" s="3">
         <v>708600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>674900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>552400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>607800</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
       </c>
@@ -999,27 +1025,30 @@
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E18" s="3">
         <v>98100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>55100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>39700</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1032,9 +1061,12 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,26 +1080,27 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-500</v>
+        <v>700</v>
       </c>
       <c r="E20" s="3">
         <v>-500</v>
       </c>
       <c r="F20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G20" s="3">
         <v>-900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-28200</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1080,27 +1113,30 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>129800</v>
+      </c>
+      <c r="E21" s="3">
         <v>172300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>133000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>63900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>89500</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1113,27 +1149,30 @@
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>59400</v>
+      </c>
+      <c r="E22" s="3">
         <v>32100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>73200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>75100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>81000</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1146,27 +1185,30 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E23" s="3">
         <v>65500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-18600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-88100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-69500</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1179,27 +1221,30 @@
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-79100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>900</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1212,9 +1257,12 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,27 +1293,30 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E26" s="3">
         <v>144600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-21300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-92100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-70500</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1278,27 +1329,30 @@
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E27" s="3">
         <v>144600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-21300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-92100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-70500</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1311,9 +1365,12 @@
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,9 +1401,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1377,9 +1437,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1473,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,27 +1509,30 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>500</v>
+        <v>-700</v>
       </c>
       <c r="E32" s="3">
         <v>500</v>
       </c>
       <c r="F32" s="3">
+        <v>500</v>
+      </c>
+      <c r="G32" s="3">
         <v>900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>28200</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1476,27 +1545,30 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E33" s="3">
         <v>144600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-21300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-92100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-70500</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1509,9 +1581,12 @@
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,27 +1617,30 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E35" s="3">
         <v>144600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-21300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-92100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-70500</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1575,32 +1653,35 @@
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1613,9 +1694,12 @@
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1713,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,26 +1729,27 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>123400</v>
+      </c>
+      <c r="E41" s="3">
         <v>162100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>111000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>19100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13000</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1676,9 +1762,12 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1709,27 +1798,30 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>120700</v>
+      </c>
+      <c r="E43" s="3">
         <v>136700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>142500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>107800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>98500</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1742,9 +1834,12 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1775,27 +1870,30 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E45" s="3">
         <v>20100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>23800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>23200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>27800</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,27 +1906,30 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>263700</v>
+      </c>
+      <c r="E46" s="3">
         <v>318800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>277300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>150100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>139300</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1841,9 +1942,12 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1874,27 +1978,30 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E48" s="3">
         <v>17500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23900</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1907,27 +2014,30 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1171100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1176300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1209000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1268800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1322200</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
       </c>
@@ -1940,9 +2050,12 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2086,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,27 +2122,30 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E52" s="3">
         <v>93200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>26300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16500</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2039,9 +2158,12 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,27 +2194,30 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1548300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1605700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1523800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1453700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1501900</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2105,9 +2230,12 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2249,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,26 +2265,27 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E57" s="3">
         <v>11600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>24600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16800</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2168,14 +2298,17 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>8300</v>
+        <v>7500</v>
       </c>
       <c r="E58" s="3">
         <v>8300</v>
@@ -2186,8 +2319,8 @@
       <c r="G58" s="3">
         <v>8300</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+      <c r="H58" s="3">
+        <v>8300</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -2201,27 +2334,30 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>130400</v>
+      </c>
+      <c r="E59" s="3">
         <v>106300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>121200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>98200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>69400</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2234,27 +2370,30 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>147400</v>
+      </c>
+      <c r="E60" s="3">
         <v>126200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>143300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>131200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>94500</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2267,27 +2406,30 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>726800</v>
+      </c>
+      <c r="E61" s="3">
         <v>683200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>688700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1013400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1008200</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2300,27 +2442,30 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>205400</v>
+      </c>
+      <c r="E62" s="3">
         <v>228000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>246100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>52200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>38100</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2333,9 +2478,12 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2514,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2550,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,27 +2586,30 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1097100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1037400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1078000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1196800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1140800</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2465,9 +2622,12 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2641,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2674,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2710,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2579,9 +2746,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,27 +2782,30 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-227300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-215800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-360400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-339100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-247000</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,9 +2818,12 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2854,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2890,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,27 +2926,30 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>451200</v>
+      </c>
+      <c r="E76" s="3">
         <v>568300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>445700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>256900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>361100</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,9 +2962,12 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,32 +2998,35 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2848,27 +3039,30 @@
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E81" s="3">
         <v>144600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-21300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-92100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-70500</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
       </c>
@@ -2881,9 +3075,12 @@
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,26 +3094,27 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E83" s="3">
         <v>74600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>78400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>76900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>78100</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
@@ -2929,9 +3127,12 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3163,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3199,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3235,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3271,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,27 +3307,30 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>90200</v>
+      </c>
+      <c r="E89" s="3">
         <v>107700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>47500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>16400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>22000</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3127,9 +3343,12 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,26 +3362,27 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6700</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,9 +3395,12 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3431,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,27 +3467,30 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-40300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-16900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21700</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3274,9 +3503,12 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,8 +3522,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3322,9 +3555,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3591,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3627,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,27 +3663,30 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-90600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-41900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>60000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-16900</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3454,27 +3699,30 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3487,27 +3735,30 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="E102" s="3">
         <v>47200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>92200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-16700</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3520,7 +3771,10 @@
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
